--- a/exports/trend_1d/GRASIM_full_report.xlsx
+++ b/exports/trend_1d/GRASIM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.27</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42060</v>
+        <v>42061</v>
       </c>
       <c r="H2" t="n">
-        <v>730.75</v>
+        <v>716.75</v>
       </c>
       <c r="I2" t="n">
         <v>726.0031728547781</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01</v>
+        <v>-1.91</v>
       </c>
       <c r="L2" t="n">
         <v>2.67</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.48</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>746.1</v>
+        <v>794.3</v>
       </c>
       <c r="I3" t="n">
         <v>784.7115457443965</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.09</v>
+        <v>-10.82</v>
       </c>
       <c r="L3" t="n">
-        <v>4.86</v>
+        <v>11.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.97</v>
+        <v>1.46</v>
       </c>
       <c r="N3" t="n">
-        <v>4.09</v>
+        <v>6.46</v>
       </c>
       <c r="O3" t="n">
         <v>-1.92</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42081</v>
+        <v>42082</v>
       </c>
       <c r="H4" t="n">
-        <v>730.95</v>
+        <v>719.55</v>
       </c>
       <c r="I4" t="n">
         <v>719.9340831523348</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.98</v>
+        <v>-9.41</v>
       </c>
       <c r="L4" t="n">
-        <v>9.31</v>
+        <v>9.84</v>
       </c>
       <c r="M4" t="n">
         <v>0.26</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.11</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42188</v>
+        <v>42191</v>
       </c>
       <c r="H5" t="n">
-        <v>698.55</v>
+        <v>709.35</v>
       </c>
       <c r="I5" t="n">
         <v>705.9350310877919</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K5" t="n">
-        <v>2.92</v>
+        <v>1.42</v>
       </c>
       <c r="L5" t="n">
         <v>5.95</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>722.2</v>
+        <v>688.1</v>
       </c>
       <c r="I6" t="n">
         <v>707.9843886668764</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>1.81</v>
+        <v>-3</v>
       </c>
       <c r="L6" t="n">
-        <v>2.58</v>
+        <v>4.49</v>
       </c>
       <c r="M6" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>4.72</v>
       </c>
       <c r="O6" t="n">
         <v>1.55</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42284</v>
+        <v>42285</v>
       </c>
       <c r="H7" t="n">
-        <v>726.05</v>
+        <v>727.95</v>
       </c>
       <c r="I7" t="n">
         <v>726.2667186007551</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.52</v>
+        <v>-5.79</v>
       </c>
       <c r="L7" t="n">
-        <v>6.1</v>
+        <v>6.31</v>
       </c>
       <c r="M7" t="n">
         <v>0.9399999999999999</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.32</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>727.6</v>
+        <v>708.6</v>
       </c>
       <c r="I8" t="n">
         <v>714.547001403611</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.05</v>
+        <v>-2.66</v>
       </c>
       <c r="L8" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="M8" t="n">
         <v>0.82</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H9" t="n">
-        <v>703.05</v>
+        <v>723.5</v>
       </c>
       <c r="I9" t="n">
         <v>705.0803095112383</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" t="n">
-        <v>0.78</v>
+        <v>-2.1</v>
       </c>
       <c r="L9" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="M9" t="n">
         <v>3.48</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42591</v>
+        <v>42592</v>
       </c>
       <c r="H10" t="n">
-        <v>1033.15</v>
+        <v>964.85</v>
       </c>
       <c r="I10" t="n">
         <v>992.100447861893</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K10" t="n">
-        <v>42.8</v>
+        <v>33.36</v>
       </c>
       <c r="L10" t="n">
         <v>3.08</v>
@@ -1011,7 +1130,7 @@
         <v>1.16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>6.61</v>
       </c>
       <c r="O10" t="n">
         <v>2.91</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.03</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42648</v>
+        <v>42649</v>
       </c>
       <c r="H11" t="n">
-        <v>982.8</v>
+        <v>1005.2</v>
       </c>
       <c r="I11" t="n">
         <v>984.2152602094704</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.86</v>
+        <v>-4.18</v>
       </c>
       <c r="L11" t="n">
         <v>7.36</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>7.45</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42675</v>
+        <v>42676</v>
       </c>
       <c r="H12" t="n">
-        <v>958.65</v>
+        <v>932.15</v>
       </c>
       <c r="I12" t="n">
         <v>948.0327897593493</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.63</v>
+        <v>-7.27</v>
       </c>
       <c r="L12" t="n">
-        <v>5.64</v>
+        <v>7.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>2.76</v>
       </c>
       <c r="O12" t="n">
         <v>2.28</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H13" t="n">
-        <v>859.35</v>
+        <v>869.85</v>
       </c>
       <c r="I13" t="n">
         <v>866.3565833052735</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K13" t="n">
-        <v>7.81</v>
+        <v>6.68</v>
       </c>
       <c r="L13" t="n">
         <v>2.79</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>1103.05</v>
+        <v>1092.55</v>
       </c>
       <c r="I14" t="n">
         <v>1093.023344116821</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K14" t="n">
-        <v>26.81</v>
+        <v>25.6</v>
       </c>
       <c r="L14" t="n">
         <v>4.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42909</v>
+        <v>42913</v>
       </c>
       <c r="H15" t="n">
-        <v>1167</v>
+        <v>1211.9</v>
       </c>
       <c r="I15" t="n">
         <v>1187.94156777088</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.81</v>
+        <v>-10.92</v>
       </c>
       <c r="L15" t="n">
-        <v>8.460000000000001</v>
+        <v>11.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
         <v>-0.95</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42934</v>
+        <v>42935</v>
       </c>
       <c r="H16" t="n">
-        <v>1302.6</v>
+        <v>1045.85</v>
       </c>
       <c r="I16" t="n">
         <v>1183.156918009678</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>7.48</v>
+        <v>-13.7</v>
       </c>
       <c r="L16" t="n">
-        <v>3.76</v>
+        <v>16.81</v>
       </c>
       <c r="M16" t="n">
-        <v>0.38</v>
+        <v>18.18</v>
       </c>
       <c r="N16" t="n">
-        <v>1.69</v>
+        <v>19.71</v>
       </c>
       <c r="O16" t="n">
         <v>3.85</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>18.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42976</v>
+        <v>42977</v>
       </c>
       <c r="H17" t="n">
-        <v>1128.35</v>
+        <v>1168.4</v>
       </c>
       <c r="I17" t="n">
         <v>1162.642397483355</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.89</v>
+        <v>-11.72</v>
       </c>
       <c r="L17" t="n">
-        <v>9.49</v>
+        <v>13.09</v>
       </c>
       <c r="M17" t="n">
         <v>1.23</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.91</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>1171.65</v>
+        <v>1136.2</v>
       </c>
       <c r="I18" t="n">
         <v>1150.184170024519</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K18" t="n">
-        <v>0.28</v>
+        <v>-2.76</v>
       </c>
       <c r="L18" t="n">
-        <v>2.94</v>
+        <v>3.54</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.23</v>
+        <v>3.03</v>
       </c>
       <c r="O18" t="n">
         <v>3.55</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.02</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43038</v>
+        <v>43039</v>
       </c>
       <c r="H19" t="n">
-        <v>1193.65</v>
+        <v>1222.25</v>
       </c>
       <c r="I19" t="n">
         <v>1214.425878626926</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.06</v>
+        <v>-7.57</v>
       </c>
       <c r="L19" t="n">
-        <v>7.39</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>8.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H20" t="n">
-        <v>1201.85</v>
+        <v>1174.15</v>
       </c>
       <c r="I20" t="n">
         <v>1188.740977741906</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.67</v>
+        <v>-3.94</v>
       </c>
       <c r="L20" t="n">
-        <v>2.95</v>
+        <v>5.17</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.83</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H21" t="n">
-        <v>1165.65</v>
+        <v>1209.4</v>
       </c>
       <c r="I21" t="n">
         <v>1196.268167934515</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>0.72</v>
+        <v>-3</v>
       </c>
       <c r="L21" t="n">
         <v>3.47</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H22" t="n">
-        <v>1184.2</v>
+        <v>1124.4</v>
       </c>
       <c r="I22" t="n">
         <v>1140.179327793101</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.08</v>
+        <v>-7.03</v>
       </c>
       <c r="L22" t="n">
-        <v>6.64</v>
+        <v>7.86</v>
       </c>
       <c r="M22" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.43</v>
+        <v>5.05</v>
       </c>
       <c r="O22" t="n">
         <v>3.75</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.45</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H23" t="n">
-        <v>981.9</v>
+        <v>1020.15</v>
       </c>
       <c r="I23" t="n">
         <v>995.6713017667544</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K23" t="n">
-        <v>12.67</v>
+        <v>9.27</v>
       </c>
       <c r="L23" t="n">
         <v>6.45</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.58</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43374</v>
+        <v>43376</v>
       </c>
       <c r="H24" t="n">
-        <v>994.75</v>
+        <v>965.65</v>
       </c>
       <c r="I24" t="n">
         <v>983.9553075276851</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.49</v>
+        <v>-5.34</v>
       </c>
       <c r="L24" t="n">
         <v>6.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.81</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43416</v>
+        <v>43417</v>
       </c>
       <c r="H25" t="n">
-        <v>857.4</v>
+        <v>872.8</v>
       </c>
       <c r="I25" t="n">
         <v>868.6789844263983</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>11.21</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>2.44</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>10.6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H26" t="n">
-        <v>822.75</v>
+        <v>791.85</v>
       </c>
       <c r="I26" t="n">
         <v>792.9808918052236</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.73</v>
+        <v>-9.27</v>
       </c>
       <c r="L26" t="n">
-        <v>9.25</v>
+        <v>9.56</v>
       </c>
       <c r="M26" t="n">
         <v>2.44</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.57</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43518</v>
+        <v>43521</v>
       </c>
       <c r="H27" t="n">
-        <v>755.7</v>
+        <v>775.55</v>
       </c>
       <c r="I27" t="n">
         <v>766.7937824641837</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
-        <v>4.57</v>
+        <v>2.06</v>
       </c>
       <c r="L27" t="n">
         <v>10.19</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.76</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43599</v>
+        <v>43600</v>
       </c>
       <c r="H28" t="n">
-        <v>842.2</v>
+        <v>811.55</v>
       </c>
       <c r="I28" t="n">
         <v>833.6260727792663</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K28" t="n">
-        <v>8.59</v>
+        <v>4.64</v>
       </c>
       <c r="L28" t="n">
         <v>3.67</v>
@@ -2037,7 +2372,7 @@
         <v>1.61</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>3.64</v>
       </c>
       <c r="O28" t="n">
         <v>2.63</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>11.36</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H29" t="n">
-        <v>883.05</v>
+        <v>906.45</v>
       </c>
       <c r="I29" t="n">
         <v>889.681453547872</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.81</v>
+        <v>-11.69</v>
       </c>
       <c r="L29" t="n">
-        <v>11.16</v>
+        <v>12.25</v>
       </c>
       <c r="M29" t="n">
         <v>1.71</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.96</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43670</v>
+        <v>43671</v>
       </c>
       <c r="H30" t="n">
-        <v>874.95</v>
+        <v>865.2</v>
       </c>
       <c r="I30" t="n">
         <v>865.6315433638292</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.48</v>
+        <v>-4.55</v>
       </c>
       <c r="L30" t="n">
         <v>6.34</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.93</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43753</v>
+        <v>43754</v>
       </c>
       <c r="H31" t="n">
-        <v>700.9</v>
+        <v>727.95</v>
       </c>
       <c r="I31" t="n">
         <v>724.8898735476181</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>18.99</v>
+        <v>15.86</v>
       </c>
       <c r="L31" t="n">
         <v>1.99</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.78</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43873</v>
+        <v>43874</v>
       </c>
       <c r="H32" t="n">
-        <v>752.35</v>
+        <v>749.25</v>
       </c>
       <c r="I32" t="n">
         <v>750.4241182884734</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="L32" t="n">
         <v>9.220000000000001</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43977</v>
+        <v>43978</v>
       </c>
       <c r="H33" t="n">
-        <v>530.55</v>
+        <v>564.4</v>
       </c>
       <c r="I33" t="n">
         <v>552.0551824099798</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K33" t="n">
-        <v>29.19</v>
+        <v>24.67</v>
       </c>
       <c r="L33" t="n">
         <v>2.48</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>15.93</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44036</v>
+        <v>44039</v>
       </c>
       <c r="H34" t="n">
-        <v>580.4</v>
+        <v>568.55</v>
       </c>
       <c r="I34" t="n">
         <v>570.8121188008668</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K34" t="n">
-        <v>2.83</v>
+        <v>0.74</v>
       </c>
       <c r="L34" t="n">
         <v>6.64</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H35" t="n">
-        <v>600.55</v>
+        <v>630.55</v>
       </c>
       <c r="I35" t="n">
         <v>628.3526571854932</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.63</v>
+        <v>-10.9</v>
       </c>
       <c r="L35" t="n">
-        <v>9.51</v>
+        <v>11.58</v>
       </c>
       <c r="M35" t="n">
         <v>0.62</v>
       </c>
       <c r="N35" t="n">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>-2.04</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.56</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44302</v>
+        <v>44305</v>
       </c>
       <c r="H36" t="n">
-        <v>1347.85</v>
+        <v>1319.45</v>
       </c>
       <c r="I36" t="n">
         <v>1339.452633376755</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K36" t="n">
-        <v>113.76</v>
+        <v>109.25</v>
       </c>
       <c r="L36" t="n">
         <v>4.91</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>9</v>
+      </c>
+      <c r="U36" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.48</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44321</v>
+        <v>44322</v>
       </c>
       <c r="H37" t="n">
-        <v>1415.25</v>
+        <v>1442.15</v>
       </c>
       <c r="I37" t="n">
         <v>1427.823776541561</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.26</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L37" t="n">
         <v>9.83</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.43</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44424</v>
+        <v>44425</v>
       </c>
       <c r="H38" t="n">
-        <v>1485</v>
+        <v>1475.15</v>
       </c>
       <c r="I38" t="n">
         <v>1482.935585326107</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K38" t="n">
-        <v>2.97</v>
+        <v>2.29</v>
       </c>
       <c r="L38" t="n">
         <v>6.72</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.96</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44446</v>
+        <v>44447</v>
       </c>
       <c r="H39" t="n">
-        <v>1548.3</v>
+        <v>1570.45</v>
       </c>
       <c r="I39" t="n">
         <v>1548.923063201038</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.96</v>
+        <v>-6.46</v>
       </c>
       <c r="L39" t="n">
-        <v>5.81</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>0.74</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.02</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H40" t="n">
-        <v>1759.75</v>
+        <v>1683.4</v>
       </c>
       <c r="I40" t="n">
         <v>1708.428162135215</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K40" t="n">
-        <v>12.05</v>
+        <v>7.19</v>
       </c>
       <c r="L40" t="n">
         <v>3.17</v>
@@ -2721,7 +3200,7 @@
         <v>1.77</v>
       </c>
       <c r="N40" t="n">
-        <v>2.51</v>
+        <v>4.34</v>
       </c>
       <c r="O40" t="n">
         <v>1.43</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.25</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H41" t="n">
-        <v>1685.3</v>
+        <v>1740.15</v>
       </c>
       <c r="I41" t="n">
         <v>1728.978880675102</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.11</v>
+        <v>-3.37</v>
       </c>
       <c r="L41" t="n">
         <v>4.71</v>
@@ -2778,7 +3269,7 @@
         <v>0.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="O41" t="n">
         <v>-4.34</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.69</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H42" t="n">
-        <v>1785</v>
+        <v>1684</v>
       </c>
       <c r="I42" t="n">
         <v>1732.476656494318</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>2.58</v>
+        <v>-3.23</v>
       </c>
       <c r="L42" t="n">
         <v>3.61</v>
@@ -2835,7 +3338,7 @@
         <v>0.41</v>
       </c>
       <c r="N42" t="n">
-        <v>3.46</v>
+        <v>5.66</v>
       </c>
       <c r="O42" t="n">
         <v>3.25</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.04</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44649</v>
+        <v>44650</v>
       </c>
       <c r="H43" t="n">
-        <v>1617.25</v>
+        <v>1661.1</v>
       </c>
       <c r="I43" t="n">
         <v>1619.490822193298</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K43" t="n">
-        <v>3.96</v>
+        <v>1.36</v>
       </c>
       <c r="L43" t="n">
         <v>5.98</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.65</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H44" t="n">
-        <v>1672.9</v>
+        <v>1615.85</v>
       </c>
       <c r="I44" t="n">
         <v>1643.660428581187</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>0.71</v>
+        <v>-2.72</v>
       </c>
       <c r="L44" t="n">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="M44" t="n">
         <v>1.68</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.42</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H45" t="n">
-        <v>1422.65</v>
+        <v>1436.5</v>
       </c>
       <c r="I45" t="n">
         <v>1424.749788123755</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K45" t="n">
-        <v>11.96</v>
+        <v>11.1</v>
       </c>
       <c r="L45" t="n">
         <v>5.01</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.17</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H46" t="n">
-        <v>1690.7</v>
+        <v>1658.85</v>
       </c>
       <c r="I46" t="n">
         <v>1672.668393618826</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K46" t="n">
-        <v>17.7</v>
+        <v>15.48</v>
       </c>
       <c r="L46" t="n">
         <v>1.68</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44895</v>
+        <v>44896</v>
       </c>
       <c r="H47" t="n">
-        <v>1752.8</v>
+        <v>1792.8</v>
       </c>
       <c r="I47" t="n">
         <v>1777.145393628444</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.66</v>
+        <v>-8.07</v>
       </c>
       <c r="L47" t="n">
-        <v>7.79</v>
+        <v>8.52</v>
       </c>
       <c r="M47" t="n">
         <v>1.92</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>7.13</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>1737.95</v>
+        <v>1702.35</v>
       </c>
       <c r="I48" t="n">
         <v>1714.527287563556</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.06</v>
+        <v>-5.05</v>
       </c>
       <c r="L48" t="n">
-        <v>4.11</v>
+        <v>5.28</v>
       </c>
       <c r="M48" t="n">
-        <v>0.44</v>
+        <v>1.14</v>
       </c>
       <c r="N48" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O48" t="n">
         <v>2.28</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.21</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H49" t="n">
-        <v>1621.5</v>
+        <v>1652.7</v>
       </c>
       <c r="I49" t="n">
         <v>1635.539345581772</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K49" t="n">
-        <v>4.75</v>
+        <v>2.92</v>
       </c>
       <c r="L49" t="n">
         <v>3.65</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45071</v>
+        <v>45072</v>
       </c>
       <c r="H50" t="n">
-        <v>1694.6</v>
+        <v>1681.6</v>
       </c>
       <c r="I50" t="n">
         <v>1682.366659002742</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K50" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="L50" t="n">
         <v>2.71</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.74</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H51" t="n">
-        <v>1727.8</v>
+        <v>1786.6</v>
       </c>
       <c r="I51" t="n">
         <v>1778.083166165849</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.75</v>
+        <v>-6.24</v>
       </c>
       <c r="L51" t="n">
         <v>6.61</v>
       </c>
       <c r="M51" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="N51" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>-0.77</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.18</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H52" t="n">
-        <v>1870</v>
+        <v>1842.25</v>
       </c>
       <c r="I52" t="n">
         <v>1866.088198361634</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K52" t="n">
-        <v>4.67</v>
+        <v>3.11</v>
       </c>
       <c r="L52" t="n">
         <v>3.37</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.51</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="H53" t="n">
-        <v>1968.05</v>
+        <v>1995.3</v>
       </c>
       <c r="I53" t="n">
         <v>1975.854879249672</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.83</v>
+        <v>-8.31</v>
       </c>
       <c r="L53" t="n">
-        <v>7.49</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M53" t="n">
         <v>0.9399999999999999</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H54" t="n">
-        <v>2368.8</v>
+        <v>2256.4</v>
       </c>
       <c r="I54" t="n">
         <v>2302.292290033725</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K54" t="n">
-        <v>18.72</v>
+        <v>13.09</v>
       </c>
       <c r="L54" t="n">
         <v>1.11</v>
       </c>
       <c r="M54" t="n">
-        <v>0.73</v>
+        <v>1.38</v>
       </c>
       <c r="N54" t="n">
-        <v>3.87</v>
+        <v>4.75</v>
       </c>
       <c r="O54" t="n">
         <v>1.38</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>8</v>
+      </c>
+      <c r="U54" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.61</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45462</v>
+        <v>45463</v>
       </c>
       <c r="H55" t="n">
-        <v>2447.15</v>
+        <v>2498.8</v>
       </c>
       <c r="I55" t="n">
         <v>2492.124017147552</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.449999999999999</v>
+        <v>-10.74</v>
       </c>
       <c r="L55" t="n">
         <v>11.85</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>9.33</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H56" t="n">
-        <v>2706.8</v>
+        <v>2612.25</v>
       </c>
       <c r="I56" t="n">
         <v>2657.664660061745</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K56" t="n">
-        <v>8.32</v>
+        <v>4.54</v>
       </c>
       <c r="L56" t="n">
         <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="N56" t="n">
-        <v>2.18</v>
+        <v>3.49</v>
       </c>
       <c r="O56" t="n">
         <v>2.11</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45525</v>
+        <v>45526</v>
       </c>
       <c r="H57" t="n">
-        <v>2684.85</v>
+        <v>2755.15</v>
       </c>
       <c r="I57" t="n">
         <v>2714.534056542615</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.78</v>
+        <v>-5.47</v>
       </c>
       <c r="L57" t="n">
-        <v>3.05</v>
+        <v>6.15</v>
       </c>
       <c r="M57" t="n">
         <v>1.13</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45597</v>
+        <v>45600</v>
       </c>
       <c r="H58" t="n">
-        <v>2698.9</v>
+        <v>2590.6</v>
       </c>
       <c r="I58" t="n">
         <v>2613.645715596075</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.04</v>
+        <v>-5.97</v>
       </c>
       <c r="L58" t="n">
-        <v>6.21</v>
+        <v>6.43</v>
       </c>
       <c r="M58" t="n">
         <v>0.58</v>
       </c>
       <c r="N58" t="n">
-        <v>2.31</v>
+        <v>4.01</v>
       </c>
       <c r="O58" t="n">
         <v>2.62</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.59</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H59" t="n">
-        <v>2606.25</v>
+        <v>2693.55</v>
       </c>
       <c r="I59" t="n">
         <v>2690.459429807222</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.6</v>
+        <v>-3.97</v>
       </c>
       <c r="L59" t="n">
-        <v>4.22</v>
+        <v>4.57</v>
       </c>
       <c r="M59" t="n">
         <v>0.63</v>
       </c>
       <c r="N59" t="n">
-        <v>2.52</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
         <v>-4.01</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.23</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H60" t="n">
-        <v>2539.05</v>
+        <v>2488.7</v>
       </c>
       <c r="I60" t="n">
         <v>2529.40292753173</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.74</v>
+        <v>-7.61</v>
       </c>
       <c r="L60" t="n">
-        <v>6.17</v>
+        <v>7.94</v>
       </c>
       <c r="M60" t="n">
         <v>0.93</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.75</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="H61" t="n">
-        <v>2461.15</v>
+        <v>2490.75</v>
       </c>
       <c r="I61" t="n">
         <v>2490.07089146445</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>1.11</v>
+        <v>-0.08</v>
       </c>
       <c r="L61" t="n">
         <v>2.99</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>7.31</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H62" t="n">
-        <v>2339.95</v>
+        <v>2306.65</v>
       </c>
       <c r="I62" t="n">
         <v>2333.132036890112</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.05</v>
+        <v>-7.39</v>
       </c>
       <c r="L62" t="n">
-        <v>6.97</v>
+        <v>7.59</v>
       </c>
       <c r="M62" t="n">
         <v>0.93</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H63" t="n">
-        <v>2469.4</v>
+        <v>2513.2</v>
       </c>
       <c r="I63" t="n">
         <v>2499.397922066941</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.06</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>9.02</v>
+        <v>10.29</v>
       </c>
       <c r="M63" t="n">
         <v>0.95</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.27</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45803</v>
+        <v>45804</v>
       </c>
       <c r="H64" t="n">
-        <v>2656.4</v>
+        <v>2614.2</v>
       </c>
       <c r="I64" t="n">
         <v>2615.087237360294</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K64" t="n">
-        <v>5.7</v>
+        <v>4.02</v>
       </c>
       <c r="L64" t="n">
         <v>1.9</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.07</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="H65" t="n">
-        <v>2708</v>
+        <v>2722.2</v>
       </c>
       <c r="I65" t="n">
         <v>2711.979717986053</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.59</v>
+        <v>-4.13</v>
       </c>
       <c r="L65" t="n">
         <v>4.89</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.36</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H66" t="n">
-        <v>2743.7</v>
+        <v>2691.6</v>
       </c>
       <c r="I66" t="n">
         <v>2699.01621662375</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K66" t="n">
-        <v>0.79</v>
+        <v>-1.12</v>
       </c>
       <c r="L66" t="n">
         <v>3.17</v>
@@ -4203,7 +4994,7 @@
         <v>1.38</v>
       </c>
       <c r="N66" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O66" t="n">
         <v>0.52</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.54</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="H67" t="n">
-        <v>2864.9</v>
+        <v>2881.2</v>
       </c>
       <c r="I67" t="n">
         <v>2867.666166320748</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.44</v>
+        <v>-7.04</v>
       </c>
       <c r="L67" t="n">
-        <v>7.13</v>
+        <v>7.68</v>
       </c>
       <c r="M67" t="n">
         <v>1.28</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.2</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H68" t="n">
-        <v>2882</v>
+        <v>2700.1</v>
       </c>
       <c r="I68" t="n">
         <v>2806.631172568408</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K68" t="n">
-        <v>0.03</v>
+        <v>-6.29</v>
       </c>
       <c r="L68" t="n">
-        <v>6.27</v>
+        <v>6.57</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.95</v>
       </c>
       <c r="N68" t="n">
-        <v>2.34</v>
+        <v>6.31</v>
       </c>
       <c r="O68" t="n">
         <v>0.57</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H69" t="n">
-        <v>2797.8</v>
+        <v>2836.7</v>
       </c>
       <c r="I69" t="n">
         <v>2831.665624226198</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.62</v>
+        <v>-5.06</v>
       </c>
       <c r="L69" t="n">
-        <v>3.8</v>
+        <v>5.37</v>
       </c>
       <c r="M69" t="n">
         <v>0.91</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.16</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H70" t="n">
-        <v>2780</v>
+        <v>2713.6</v>
       </c>
       <c r="I70" t="n">
         <v>2743.583817654087</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K70" t="n">
-        <v>-2</v>
+        <v>-4.34</v>
       </c>
       <c r="L70" t="n">
-        <v>3.47</v>
+        <v>4.61</v>
       </c>
       <c r="M70" t="n">
         <v>0.57</v>
       </c>
       <c r="N70" t="n">
-        <v>1.59</v>
+        <v>2.39</v>
       </c>
       <c r="O70" t="n">
         <v>1.39</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>7.04</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H71" t="n">
-        <v>2836.9</v>
+        <v>2926.3</v>
       </c>
       <c r="I71" t="n">
         <v>2883.921942742256</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.54</v>
+        <v>-7.84</v>
       </c>
       <c r="L71" t="n">
-        <v>6.54</v>
+        <v>8.34</v>
       </c>
       <c r="M71" t="n">
         <v>3.4</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.86</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H72" t="n">
-        <v>2777.3</v>
+        <v>2683.2</v>
       </c>
       <c r="I72" t="n">
         <v>2750.684263872159</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.09</v>
+        <v>-8.31</v>
       </c>
       <c r="L72" t="n">
-        <v>7.86</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M72" t="n">
         <v>2.5</v>
       </c>
       <c r="N72" t="n">
-        <v>2.37</v>
+        <v>3.39</v>
       </c>
       <c r="O72" t="n">
         <v>3.15</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>8.23</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H73" t="n">
-        <v>2760.1</v>
+        <v>2777.7</v>
       </c>
       <c r="I73" t="n">
         <v>2777.693451548782</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.87</v>
+        <v>-3.52</v>
       </c>
       <c r="L73" t="n">
         <v>4.16</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>7.66</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H74" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="I74" t="n">
         <v>3120.911906022088</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K74" t="n">
-        <v>13.4</v>
+        <v>11.6</v>
       </c>
       <c r="L74" t="n">
         <v>1.83</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>6</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>20</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.4</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="11">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.33</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.64</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>113.76</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.28</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.89</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.85</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -9857,7 +10764,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="25">
@@ -9877,7 +10784,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.18</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="26">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.55</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="27">
@@ -9897,7 +10804,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.04</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="28">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
